--- a/Aji_game copy.xlsx
+++ b/Aji_game copy.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sboora01/Ajinomoto_agents_pptx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sboora01/AJi_game project/Ajinomoto-conductor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4C399D1-8CE8-164F-BED0-784B91318CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F6FAC39-DC23-4541-839B-5B65129D3DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2240" yWindow="-19460" windowWidth="30240" windowHeight="17860" xr2:uid="{21F6189A-E587-BD42-BB90-C9E09379CDC7}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="4" xr2:uid="{21F6189A-E587-BD42-BB90-C9E09379CDC7}"/>
   </bookViews>
   <sheets>
     <sheet name="User_funnel" sheetId="1" r:id="rId1"/>
@@ -24,9 +24,6 @@
   <definedNames>
     <definedName name="_xlchart.v2.0" hidden="1">User_funnel!$A$2:$A$4</definedName>
     <definedName name="_xlchart.v2.1" hidden="1">User_funnel!$C$2:$C$4</definedName>
-    <definedName name="_xlchart.v2.2" hidden="1">User_funnel!$A$2:$A$4</definedName>
-    <definedName name="_xlchart.v2.3" hidden="1">User_funnel!$B$1</definedName>
-    <definedName name="_xlchart.v2.4" hidden="1">User_funnel!$B$2:$B$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="127">
   <si>
     <t>event</t>
   </si>
@@ -368,533 +365,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>DATE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3C4043"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>updated_at</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3C4043"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202124"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF1967D2"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>as</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202124"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>update_date</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202124"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SUM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3C4043"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>score</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3C4043"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202124"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF1967D2"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>as</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202124"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>total_score</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>from</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202124"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>`dentsu-merkle-ajt.ajt_game_dataset_test.gameplay_report`</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>GROUP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202124"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF1967D2"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>BY</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202124"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ORDER</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202124"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF1967D2"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>BY</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202124"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202124"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF1967D2"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>ASC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202124"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">; </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SUM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3C4043"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>duration_minutes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3C4043"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202124"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF1967D2"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>AS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202124"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>total_duration</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202124"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SUM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3C4043"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF1967D2"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>ROUND</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3C4043"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>duration_minutes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202124"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3C4043"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202124"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFB06000"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3C4043"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202124"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF1967D2"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>AS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202124"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>total_duration_sec</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202124"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFB80672"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>-- Group ตาม update_date</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202124"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF1967D2"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>ASC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202124"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFB80672"/>
-        <rFont val="Menlo"/>
-        <family val="2"/>
-      </rPr>
-      <t>-- เรียงจากวันที่ล่าสุด</t>
     </r>
   </si>
   <si>
@@ -1316,9 +786,6 @@
     </r>
   </si>
   <si>
-    <t>from slide</t>
-  </si>
-  <si>
     <t>avg(March)</t>
   </si>
   <si>
@@ -1331,10 +798,32 @@
     <t>Avg (March)</t>
   </si>
   <si>
-    <t>average</t>
+    <t>Month</t>
   </si>
   <si>
-    <t>Month</t>
+    <t>February</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>Average user</t>
+  </si>
+  <si>
+    <t>user stickiness average</t>
+  </si>
+  <si>
+    <t>Average total score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sum_total_score
+</t>
+  </si>
+  <si>
+    <t>Average total_duration_min</t>
+  </si>
+  <si>
+    <t>sum_total_duration_min</t>
   </si>
 </sst>
 </file>
@@ -1344,7 +833,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0,&quot;k&quot;"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1397,12 +886,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFB80672"/>
-      <name val="Menlo"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF188038"/>
       <name val="Menlo"/>
       <family val="2"/>
@@ -1428,7 +911,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1447,6 +930,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10231,13 +9718,13 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>119</v>
       </c>
       <c r="C5" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -10264,18 +9751,12 @@
       <c r="D1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" t="s">
-        <v>125</v>
-      </c>
+      <c r="H1" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
@@ -10287,21 +9768,20 @@
       <c r="C2">
         <v>0</v>
       </c>
-      <c r="E2">
-        <f>AVERAGE(D5:D35)</f>
-        <v>7.67741935483871</v>
-      </c>
-      <c r="F2">
-        <f>AVERAGE(D36:D66)</f>
-        <v>5.67741935483871</v>
-      </c>
-      <c r="G2">
-        <f>AVERAGE(D67:D94)</f>
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <f>AVERAGE(D95:D123)</f>
-        <v>2.9655172413793105</v>
+      <c r="G2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -10314,6 +9794,25 @@
       <c r="C3">
         <v>2</v>
       </c>
+      <c r="G3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H3">
+        <f>AVERAGE(D5:D35)</f>
+        <v>7.67741935483871</v>
+      </c>
+      <c r="I3">
+        <f>AVERAGE(D36:D66)</f>
+        <v>5.67741935483871</v>
+      </c>
+      <c r="J3">
+        <f>AVERAGE(D67:D94)</f>
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <f>AVERAGE(D95:D123)</f>
+        <v>2.9655172413793105</v>
+      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -10356,7 +9855,7 @@
         <v>6</v>
       </c>
       <c r="H6" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="I6" t="s">
         <v>7</v>
@@ -10368,7 +9867,7 @@
         <v>9</v>
       </c>
       <c r="L6" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="34" x14ac:dyDescent="0.2">
@@ -10480,7 +9979,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>45998</v>
       </c>
@@ -10494,14 +9993,9 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I11">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>45999</v>
       </c>
@@ -10515,7 +10009,13 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H12" s="2"/>
+      <c r="H12" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I12">
+        <f>AVERAGE(I9:L9)</f>
+        <v>9.9402112338999444</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
@@ -10561,13 +10061,6 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="H15" t="s">
-        <v>129</v>
-      </c>
-      <c r="I15">
-        <f>AVERAGE(I9:L9)</f>
-        <v>9.9402112338999444</v>
-      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
@@ -12190,6 +11683,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:K1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -12197,7 +11693,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D661A788-0182-C446-91FA-D86185AF7F82}">
-  <dimension ref="A1:H126"/>
+  <dimension ref="A1:H124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -12217,15 +11713,11 @@
       <c r="C1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>127</v>
-      </c>
+      <c r="F1" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
@@ -12237,17 +11729,18 @@
       <c r="C2" s="8">
         <v>22648</v>
       </c>
-      <c r="D2" s="3">
-        <f>AVERAGE(C36:C66)</f>
-        <v>87248.290322580651</v>
-      </c>
-      <c r="E2" s="3">
-        <f>AVERAGE(C67:C94)</f>
-        <v>28986.392857142859</v>
-      </c>
-      <c r="F2" s="3">
-        <f>AVERAGE(C95:C124)</f>
-        <v>12265.766666666666</v>
+      <c r="D2" s="3"/>
+      <c r="E2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -12260,6 +11753,21 @@
       <c r="C3" s="8">
         <v>17590</v>
       </c>
+      <c r="E3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" s="3">
+        <f>AVERAGE(B36:B66)</f>
+        <v>87248.290322580651</v>
+      </c>
+      <c r="G3" s="3">
+        <f>AVERAGE(B67:B94)</f>
+        <v>28986.392857142859</v>
+      </c>
+      <c r="H3" s="3">
+        <f>AVERAGE(B95:B124)</f>
+        <v>12265.766666666666</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
@@ -12271,9 +11779,7 @@
       <c r="C4" s="8">
         <v>23611</v>
       </c>
-      <c r="H4" s="13" t="s">
-        <v>102</v>
-      </c>
+      <c r="H4" s="13"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
@@ -12285,9 +11791,7 @@
       <c r="C5" s="8">
         <v>69299</v>
       </c>
-      <c r="H5" s="13" t="s">
-        <v>103</v>
-      </c>
+      <c r="H5" s="13"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
@@ -12299,9 +11803,10 @@
       <c r="C6" s="8">
         <v>49006</v>
       </c>
-      <c r="H6" s="13" t="s">
-        <v>104</v>
-      </c>
+      <c r="E6" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="H6" s="13"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
@@ -12313,9 +11818,11 @@
       <c r="C7" s="8">
         <v>60593</v>
       </c>
-      <c r="H7" s="13" t="s">
-        <v>105</v>
-      </c>
+      <c r="E7" s="3">
+        <f>SUM(C2:C124)</f>
+        <v>7796142</v>
+      </c>
+      <c r="H7" s="13"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
@@ -12327,9 +11834,7 @@
       <c r="C8" s="8">
         <v>112498</v>
       </c>
-      <c r="H8" s="13" t="s">
-        <v>106</v>
-      </c>
+      <c r="H8" s="13"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
@@ -12341,9 +11846,7 @@
       <c r="C9" s="8">
         <v>145294</v>
       </c>
-      <c r="H9" s="14">
-        <v>1</v>
-      </c>
+      <c r="H9" s="14"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
@@ -12355,9 +11858,7 @@
       <c r="C10" s="8">
         <v>78938</v>
       </c>
-      <c r="H10" s="13" t="s">
-        <v>107</v>
-      </c>
+      <c r="H10" s="13"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
@@ -12369,9 +11870,7 @@
       <c r="C11" s="8">
         <v>56748</v>
       </c>
-      <c r="H11" s="14" t="s">
-        <v>108</v>
-      </c>
+      <c r="H11" s="14"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
@@ -12780,7 +12279,7 @@
         <v>95455</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="5">
         <v>46036</v>
       </c>
@@ -12791,7 +12290,7 @@
         <v>117061</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="5">
         <v>46037</v>
       </c>
@@ -12802,7 +12301,7 @@
         <v>77079</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="5">
         <v>46038</v>
       </c>
@@ -12813,7 +12312,7 @@
         <v>82669</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="5">
         <v>46039</v>
       </c>
@@ -12824,7 +12323,7 @@
         <v>74776</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="5">
         <v>46040</v>
       </c>
@@ -12835,7 +12334,7 @@
         <v>90533</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" s="5">
         <v>46041</v>
       </c>
@@ -12846,7 +12345,7 @@
         <v>64761</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" s="5">
         <v>46042</v>
       </c>
@@ -12857,7 +12356,7 @@
         <v>70712</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" s="5">
         <v>46043</v>
       </c>
@@ -12868,7 +12367,7 @@
         <v>91045</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <v>46044</v>
       </c>
@@ -12879,7 +12378,7 @@
         <v>122687</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>46045</v>
       </c>
@@ -12889,12 +12388,8 @@
       <c r="C58" s="8">
         <v>55661</v>
       </c>
-      <c r="F58">
-        <f>+F30</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>46046</v>
       </c>
@@ -12905,7 +12400,7 @@
         <v>69876</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>46047</v>
       </c>
@@ -12916,7 +12411,7 @@
         <v>51679</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>46048</v>
       </c>
@@ -12927,7 +12422,7 @@
         <v>49703</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" s="5">
         <v>46049</v>
       </c>
@@ -12938,7 +12433,7 @@
         <v>40681</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" s="5">
         <v>46050</v>
       </c>
@@ -12949,7 +12444,7 @@
         <v>94663</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" s="5">
         <v>46051</v>
       </c>
@@ -13620,13 +13115,10 @@
         <v>4165</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C126" s="3">
-        <f>SUM(C2:C124)</f>
-        <v>7796142</v>
-      </c>
-    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:H1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
@@ -13642,7 +13134,7 @@
     <col min="3" max="4" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>37</v>
       </c>
@@ -13656,20 +13148,13 @@
         <v>41</v>
       </c>
       <c r="E1" s="6"/>
-      <c r="F1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H1" t="s">
-        <v>128</v>
-      </c>
-      <c r="I1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H1" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>45989</v>
       </c>
@@ -13684,24 +13169,21 @@
         <v>1326</v>
       </c>
       <c r="E2" s="6"/>
-      <c r="F2" s="9">
-        <f>AVERAGE(C35:C65)</f>
-        <v>86.739064516128991</v>
-      </c>
-      <c r="G2" s="9">
-        <f>AVERAGE(B67:B94)</f>
-        <v>31.964285714285715</v>
-      </c>
-      <c r="H2" s="9">
-        <f>AVERAGE(B95:B124)</f>
-        <v>14.933333333333334</v>
-      </c>
-      <c r="I2" s="9">
-        <f>SUM(C1:C124)</f>
-        <v>7875.5110999999924</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F2" s="9"/>
+      <c r="G2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>45990</v>
       </c>
@@ -13716,8 +13198,23 @@
         <v>907</v>
       </c>
       <c r="E3" s="6"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="9">
+        <f>AVERAGE(C35:C65)</f>
+        <v>86.739064516128991</v>
+      </c>
+      <c r="I3" s="9">
+        <f>AVERAGE(B67:B94)</f>
+        <v>31.964285714285715</v>
+      </c>
+      <c r="J3" s="9">
+        <f>AVERAGE(B95:B124)</f>
+        <v>14.933333333333334</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>45991</v>
       </c>
@@ -13733,7 +13230,7 @@
       </c>
       <c r="E4" s="6"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>45992</v>
       </c>
@@ -13748,8 +13245,11 @@
         <v>3731</v>
       </c>
       <c r="E5" s="6"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>45993</v>
       </c>
@@ -13764,8 +13264,12 @@
         <v>3435</v>
       </c>
       <c r="E6" s="6"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F6" s="9">
+        <f>SUM(C2:C124)</f>
+        <v>7875.5110999999924</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>45994</v>
       </c>
@@ -13780,8 +13284,9 @@
         <v>4329</v>
       </c>
       <c r="E7" s="6"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>45995</v>
       </c>
@@ -13797,7 +13302,7 @@
       </c>
       <c r="E8" s="6"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>45996</v>
       </c>
@@ -13813,7 +13318,7 @@
       </c>
       <c r="E9" s="6"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>45997</v>
       </c>
@@ -13829,7 +13334,7 @@
       </c>
       <c r="E10" s="6"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>45998</v>
       </c>
@@ -13845,7 +13350,7 @@
       </c>
       <c r="E11" s="6"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>45999</v>
       </c>
@@ -13861,7 +13366,7 @@
       </c>
       <c r="E12" s="6"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>46000</v>
       </c>
@@ -13877,7 +13382,7 @@
       </c>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>46001</v>
       </c>
@@ -13893,7 +13398,7 @@
       </c>
       <c r="E14" s="6"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>46002</v>
       </c>
@@ -13909,7 +13414,7 @@
       </c>
       <c r="E15" s="6"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>46003</v>
       </c>
@@ -14148,9 +13653,7 @@
         <v>7845</v>
       </c>
       <c r="E30" s="6"/>
-      <c r="M30" s="13" t="s">
-        <v>102</v>
-      </c>
+      <c r="M30" s="13"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
@@ -14167,9 +13670,7 @@
         <v>5571</v>
       </c>
       <c r="E31" s="6"/>
-      <c r="M31" s="13" t="s">
-        <v>103</v>
-      </c>
+      <c r="M31" s="13"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="5">
@@ -14186,9 +13687,7 @@
         <v>8638</v>
       </c>
       <c r="E32" s="6"/>
-      <c r="M32" s="13" t="s">
-        <v>109</v>
-      </c>
+      <c r="M32" s="13"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="5">
@@ -14205,9 +13704,7 @@
         <v>8234</v>
       </c>
       <c r="E33" s="6"/>
-      <c r="M33" s="13" t="s">
-        <v>110</v>
-      </c>
+      <c r="M33" s="13"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="5">
@@ -14224,9 +13721,7 @@
         <v>7879</v>
       </c>
       <c r="E34" s="6"/>
-      <c r="M34" s="13" t="s">
-        <v>105</v>
-      </c>
+      <c r="M34" s="13"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" s="5">
@@ -14243,9 +13738,7 @@
         <v>6524</v>
       </c>
       <c r="E35" s="6"/>
-      <c r="M35" s="13" t="s">
-        <v>106</v>
-      </c>
+      <c r="M35" s="13"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="5">
@@ -14262,9 +13755,7 @@
         <v>6350</v>
       </c>
       <c r="E36" s="6"/>
-      <c r="M36" s="14" t="s">
-        <v>111</v>
-      </c>
+      <c r="M36" s="14"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="5">
@@ -14281,9 +13772,7 @@
         <v>9001</v>
       </c>
       <c r="E37" s="6"/>
-      <c r="M37" s="13" t="s">
-        <v>107</v>
-      </c>
+      <c r="M37" s="13"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" s="5">
@@ -14300,9 +13789,7 @@
         <v>4515</v>
       </c>
       <c r="E38" s="6"/>
-      <c r="M38" s="14" t="s">
-        <v>112</v>
-      </c>
+      <c r="M38" s="14"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="5">
@@ -15652,6 +15139,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:J1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -15739,7 +15229,7 @@
     </row>
     <row r="41" spans="8:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="H41" s="2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -16203,7 +15693,7 @@
     </row>
     <row r="59" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
       <c r="J59" s="2" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -16345,47 +15835,47 @@
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" s="15" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" s="15" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" s="13" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" s="13" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" s="13" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" s="13" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" s="13" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" s="13" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="13" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
